--- a/Result/profitability/3498.xlsx
+++ b/Result/profitability/3498.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07375</v>
+        <v>0.485</v>
       </c>
       <c r="N2" t="n">
-        <v>32.72875</v>
+        <v>34.73</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009999999999999988</v>
+        <v>0.47875</v>
       </c>
       <c r="N3" t="n">
-        <v>32.0025</v>
+        <v>33.535</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.78</v>
       </c>
       <c r="M4" t="n">
-        <v>0.14375</v>
+        <v>0.7075</v>
       </c>
       <c r="N4" t="n">
-        <v>31.9</v>
+        <v>36.27875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.56</v>
       </c>
       <c r="M5" t="n">
-        <v>0.595</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>36.065</v>
+        <v>36.96875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1030,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.71</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6412500000000001</v>
+        <v>1.0975</v>
       </c>
       <c r="N6" t="n">
-        <v>35.78375</v>
+        <v>35.9325</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7524999999999999</v>
+        <v>1.0125</v>
       </c>
       <c r="N7" t="n">
-        <v>34.55625</v>
+        <v>35.21875</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>0.11</v>
       </c>
       <c r="M8" t="n">
-        <v>0.59375</v>
+        <v>1.05125</v>
       </c>
       <c r="N8" t="n">
-        <v>33.33875</v>
+        <v>35.89</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>-0.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0.31375</v>
+        <v>0.3137500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>26.7375</v>
@@ -2026,7 +2026,7 @@
         <v>-0.53</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.07250000000000001</v>
+        <v>-0.07249999999999995</v>
       </c>
       <c r="N13" t="n">
         <v>23.175</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3498</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>814</v>
+      </c>
+      <c r="D75" t="n">
+        <v>436</v>
+      </c>
+      <c r="E75" t="n">
+        <v>378</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>239</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>29.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>256</v>
+      </c>
+      <c r="K75" t="n">
+        <v>209</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.27125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.7837941628264211</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>9.176470588235293</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.230000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1843447220805712</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
